--- a/Backtest/01-07-22/S&P500stock_01-07-22period252RS90.xlsx
+++ b/Backtest/01-07-22/S&P500stock_01-07-22period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="101">
   <si>
     <t>Stock</t>
   </si>
@@ -124,16 +124,199 @@
     <t>Industry</t>
   </si>
   <si>
-    <t>PFE</t>
-  </si>
-  <si>
-    <t>2022-07-28</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers - General</t>
+    <t>EM Rating</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>WFC</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>LYV</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>SPG</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>AZO</t>
+  </si>
+  <si>
+    <t>RJF</t>
+  </si>
+  <si>
+    <t>PLD</t>
+  </si>
+  <si>
+    <t>EXR</t>
+  </si>
+  <si>
+    <t>CBRE</t>
+  </si>
+  <si>
+    <t>PSA</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>2022-02-24</t>
+  </si>
+  <si>
+    <t>2022-01-27</t>
+  </si>
+  <si>
+    <t>2022-03-01</t>
+  </si>
+  <si>
+    <t>2022-02-03</t>
+  </si>
+  <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
+    <t>2022-02-07</t>
+  </si>
+  <si>
+    <t>2022-02-10</t>
+  </si>
+  <si>
+    <t>2022-02-02</t>
+  </si>
+  <si>
+    <t>2022-01-14</t>
+  </si>
+  <si>
+    <t>2022-02-22</t>
+  </si>
+  <si>
+    <t>2022-02-23</t>
+  </si>
+  <si>
+    <t>2022-01-26</t>
+  </si>
+  <si>
+    <t>2022-02-16</t>
+  </si>
+  <si>
+    <t>2022-01-19</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>REIT - Retail</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Banks - Diversified</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Specialty Retail</t>
+  </si>
+  <si>
+    <t>REIT - Industrial</t>
+  </si>
+  <si>
+    <t>Real Estate Services</t>
+  </si>
+  <si>
+    <t>REIT - Residential</t>
   </si>
 </sst>
 </file>
@@ -491,10 +674,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,43 +786,52 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>95.16129032258065</v>
+        <v>93.54838709677419</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="D2">
-        <v>52.43</v>
+        <v>95.52</v>
       </c>
       <c r="E2">
-        <v>2.25</v>
+        <v>2.17</v>
+      </c>
+      <c r="F2">
+        <v>0.03518941283468211</v>
       </c>
       <c r="G2">
-        <v>1.93</v>
+        <v>2.22</v>
+      </c>
+      <c r="H2">
+        <v>0.196218498523353</v>
       </c>
       <c r="I2">
-        <v>51.5</v>
+        <v>92.89199981689453</v>
       </c>
       <c r="J2">
-        <v>50.57199974060059</v>
+        <v>88.78549995422364</v>
       </c>
       <c r="K2">
-        <v>50.54480003356934</v>
+        <v>90.14679977416992</v>
       </c>
       <c r="L2">
-        <v>50.36910003662109</v>
+        <v>80.69079986572265</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -663,46 +855,2689 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>50.08</v>
+      </c>
+      <c r="Y2">
+        <v>98.2</v>
+      </c>
+      <c r="Z2">
+        <v>46.88</v>
+      </c>
+      <c r="AA2">
+        <v>-16.61</v>
+      </c>
+      <c r="AB2">
+        <v>8550</v>
+      </c>
+      <c r="AC2">
+        <v>224.14</v>
+      </c>
+      <c r="AD2">
+        <v>5.03</v>
+      </c>
+      <c r="AE2">
+        <v>20.51</v>
+      </c>
+      <c r="AF2">
+        <v>33.33</v>
+      </c>
+      <c r="AG2">
+        <v>101.72</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK2">
+        <v>84.15280933772154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3">
+        <v>98.99193548387096</v>
+      </c>
+      <c r="C3">
+        <v>147</v>
+      </c>
+      <c r="D3">
+        <v>116.6</v>
+      </c>
+      <c r="E3">
+        <v>3.49</v>
+      </c>
+      <c r="F3">
+        <v>1.670753671348052</v>
+      </c>
+      <c r="G3">
+        <v>2.87</v>
+      </c>
+      <c r="H3">
+        <v>1.177310991140116</v>
+      </c>
+      <c r="I3">
+        <v>116.7160003662109</v>
+      </c>
+      <c r="J3">
+        <v>114.7599998474121</v>
+      </c>
+      <c r="K3">
+        <v>112.8603997802734</v>
+      </c>
+      <c r="L3">
+        <v>102.7784997940064</v>
+      </c>
+      <c r="M3">
+        <v>1.02</v>
+      </c>
+      <c r="N3">
+        <v>1.03</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>47.94</v>
+      </c>
+      <c r="Y3">
+        <v>128.81</v>
+      </c>
+      <c r="Z3">
+        <v>28.68</v>
+      </c>
+      <c r="AA3">
+        <v>166.14</v>
+      </c>
+      <c r="AB3">
+        <v>515.8099999999999</v>
+      </c>
+      <c r="AC3">
+        <v>456.49</v>
+      </c>
+      <c r="AD3">
+        <v>15.94</v>
+      </c>
+      <c r="AE3">
+        <v>44.36</v>
+      </c>
+      <c r="AF3">
+        <v>62.9</v>
+      </c>
+      <c r="AG3">
+        <v>136.64</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK3">
+        <v>78.42310610283324</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>98.58870967741935</v>
+      </c>
+      <c r="C4">
+        <v>191</v>
+      </c>
+      <c r="D4">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="E4">
+        <v>2.24</v>
+      </c>
+      <c r="F4">
+        <v>0.1219238810891793</v>
+      </c>
+      <c r="G4">
+        <v>2.27</v>
+      </c>
+      <c r="H4">
+        <v>0.2716871518015653</v>
+      </c>
+      <c r="I4">
+        <v>83.89599914550782</v>
+      </c>
+      <c r="J4">
+        <v>80.9060001373291</v>
+      </c>
+      <c r="K4">
+        <v>73.13960006713867</v>
+      </c>
+      <c r="L4">
+        <v>54.72195001602173</v>
+      </c>
+      <c r="M4">
+        <v>1.04</v>
+      </c>
+      <c r="N4">
+        <v>1.15</v>
+      </c>
+      <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="U4" t="b">
         <v>1</v>
       </c>
-      <c r="X2">
-        <v>38.93</v>
-      </c>
-      <c r="Y2">
-        <v>61.71</v>
-      </c>
-      <c r="Z2">
-        <v>298.09</v>
-      </c>
-      <c r="AA2">
-        <v>29.74</v>
-      </c>
-      <c r="AB2">
-        <v>52.92</v>
-      </c>
-      <c r="AC2">
-        <v>41.41</v>
-      </c>
-      <c r="AD2">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="AE2">
-        <v>129.51</v>
-      </c>
-      <c r="AF2">
-        <v>-57.93</v>
-      </c>
-      <c r="AG2">
-        <v>46.46</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>39</v>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>37.46</v>
+      </c>
+      <c r="Y4">
+        <v>86.48</v>
+      </c>
+      <c r="Z4">
+        <v>10.64</v>
+      </c>
+      <c r="AA4">
+        <v>104.94</v>
+      </c>
+      <c r="AB4">
+        <v>144.41</v>
+      </c>
+      <c r="AC4">
+        <v>152.1</v>
+      </c>
+      <c r="AD4">
+        <v>11.1</v>
+      </c>
+      <c r="AE4">
+        <v>25</v>
+      </c>
+      <c r="AF4">
+        <v>185.71</v>
+      </c>
+      <c r="AG4">
+        <v>-29.41</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK4">
+        <v>64.65869170651369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>96.16935483870968</v>
+      </c>
+      <c r="C5">
+        <v>80</v>
+      </c>
+      <c r="D5">
+        <v>78.48999999999999</v>
+      </c>
+      <c r="E5">
+        <v>2.24</v>
+      </c>
+      <c r="F5">
+        <v>0.1219238810891793</v>
+      </c>
+      <c r="G5">
+        <v>2.02</v>
+      </c>
+      <c r="H5">
+        <v>-0.1056561145894973</v>
+      </c>
+      <c r="I5">
+        <v>75.41199951171875</v>
+      </c>
+      <c r="J5">
+        <v>72.44499969482422</v>
+      </c>
+      <c r="K5">
+        <v>72.76499969482421</v>
+      </c>
+      <c r="L5">
+        <v>62.20729997634888</v>
+      </c>
+      <c r="M5">
+        <v>1.04</v>
+      </c>
+      <c r="N5">
+        <v>1.04</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>39.7</v>
+      </c>
+      <c r="Y5">
+        <v>78.79000000000001</v>
+      </c>
+      <c r="Z5">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="AA5">
+        <v>-2.07</v>
+      </c>
+      <c r="AB5">
+        <v>281.08</v>
+      </c>
+      <c r="AC5">
+        <v>343.84</v>
+      </c>
+      <c r="AD5">
+        <v>5.39</v>
+      </c>
+      <c r="AE5">
+        <v>14.84</v>
+      </c>
+      <c r="AF5">
+        <v>106.67</v>
+      </c>
+      <c r="AG5">
+        <v>202.74</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK5">
+        <v>64.26116138462454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6">
+        <v>99.79838709677419</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>48.37</v>
+      </c>
+      <c r="E6">
+        <v>3.6</v>
+      </c>
+      <c r="F6">
+        <v>1.807050692890833</v>
+      </c>
+      <c r="G6">
+        <v>3.07</v>
+      </c>
+      <c r="H6">
+        <v>1.479185604252965</v>
+      </c>
+      <c r="I6">
+        <v>46.45199966430664</v>
+      </c>
+      <c r="J6">
+        <v>42.99149990081787</v>
+      </c>
+      <c r="K6">
+        <v>42.70800018310547</v>
+      </c>
+      <c r="L6">
+        <v>32.0202500629425</v>
+      </c>
+      <c r="M6">
+        <v>1.08</v>
+      </c>
+      <c r="N6">
+        <v>1.09</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>16.11</v>
+      </c>
+      <c r="Y6">
+        <v>48.99</v>
+      </c>
+      <c r="Z6">
+        <v>24.11</v>
+      </c>
+      <c r="AA6">
+        <v>-0.38</v>
+      </c>
+      <c r="AB6">
+        <v>119.22</v>
+      </c>
+      <c r="AC6">
+        <v>559.26</v>
+      </c>
+      <c r="AD6">
+        <v>9.31</v>
+      </c>
+      <c r="AE6">
+        <v>226.32</v>
+      </c>
+      <c r="AF6">
+        <v>15.15</v>
+      </c>
+      <c r="AG6">
+        <v>222.22</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK6">
+        <v>61.71753624979871</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7">
+        <v>98.18548387096774</v>
+      </c>
+      <c r="C7">
+        <v>93</v>
+      </c>
+      <c r="D7">
+        <v>67.25</v>
+      </c>
+      <c r="E7">
+        <v>3.28</v>
+      </c>
+      <c r="F7">
+        <v>1.410550266584561</v>
+      </c>
+      <c r="G7">
+        <v>3.22</v>
+      </c>
+      <c r="H7">
+        <v>1.705591564087603</v>
+      </c>
+      <c r="I7">
+        <v>68.74199829101562</v>
+      </c>
+      <c r="J7">
+        <v>65.9299997329712</v>
+      </c>
+      <c r="K7">
+        <v>61.97259986877442</v>
+      </c>
+      <c r="L7">
+        <v>46.54709987640381</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>1.11</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>2</v>
+      </c>
+      <c r="T7">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>33.78</v>
+      </c>
+      <c r="Y7">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="Z7">
+        <v>20.17</v>
+      </c>
+      <c r="AA7">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="AB7">
+        <v>122.54</v>
+      </c>
+      <c r="AC7">
+        <v>242.86</v>
+      </c>
+      <c r="AD7">
+        <v>7.49</v>
+      </c>
+      <c r="AE7">
+        <v>67.44</v>
+      </c>
+      <c r="AF7">
+        <v>95.45</v>
+      </c>
+      <c r="AG7">
+        <v>4.76</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK7">
+        <v>61.56328505706738</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>95.36290322580645</v>
+      </c>
+      <c r="C8">
+        <v>395</v>
+      </c>
+      <c r="D8">
+        <v>76.44</v>
+      </c>
+      <c r="E8">
+        <v>1.43</v>
+      </c>
+      <c r="F8">
+        <v>-0.8817178229985704</v>
+      </c>
+      <c r="G8">
+        <v>1.54</v>
+      </c>
+      <c r="H8">
+        <v>-0.8301551860603373</v>
+      </c>
+      <c r="I8">
+        <v>76.40000152587891</v>
+      </c>
+      <c r="J8">
+        <v>73.67200088500977</v>
+      </c>
+      <c r="K8">
+        <v>73.29920028686523</v>
+      </c>
+      <c r="L8">
+        <v>67.17600011825562</v>
+      </c>
+      <c r="M8">
+        <v>1.04</v>
+      </c>
+      <c r="N8">
+        <v>1.04</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>43.49</v>
+      </c>
+      <c r="Y8">
+        <v>78.78</v>
+      </c>
+      <c r="Z8">
+        <v>11.49</v>
+      </c>
+      <c r="AA8">
+        <v>15.2</v>
+      </c>
+      <c r="AB8">
+        <v>286.27</v>
+      </c>
+      <c r="AC8">
+        <v>187.5</v>
+      </c>
+      <c r="AD8">
+        <v>1.93</v>
+      </c>
+      <c r="AE8">
+        <v>23.21</v>
+      </c>
+      <c r="AF8">
+        <v>16.67</v>
+      </c>
+      <c r="AG8">
+        <v>100</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK8">
+        <v>60.50834166708108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>24.46</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>2.302676225773672</v>
+      </c>
+      <c r="G9">
+        <v>3.18</v>
+      </c>
+      <c r="H9">
+        <v>1.645216641465033</v>
+      </c>
+      <c r="I9">
+        <v>22.9939998626709</v>
+      </c>
+      <c r="J9">
+        <v>20.93949995040894</v>
+      </c>
+      <c r="K9">
+        <v>19.91799999237061</v>
+      </c>
+      <c r="L9">
+        <v>15.20774997234344</v>
+      </c>
+      <c r="M9">
+        <v>1.1</v>
+      </c>
+      <c r="N9">
+        <v>1.15</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>8.82</v>
+      </c>
+      <c r="Y9">
+        <v>24.95</v>
+      </c>
+      <c r="Z9">
+        <v>57.15</v>
+      </c>
+      <c r="AA9">
+        <v>5.35</v>
+      </c>
+      <c r="AB9">
+        <v>196</v>
+      </c>
+      <c r="AC9">
+        <v>165.71</v>
+      </c>
+      <c r="AD9">
+        <v>4.96</v>
+      </c>
+      <c r="AE9">
+        <v>228.57</v>
+      </c>
+      <c r="AF9">
+        <v>-82.93000000000001</v>
+      </c>
+      <c r="AG9">
+        <v>217.14</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK9">
+        <v>57.21872076455294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <v>91.53225806451613</v>
+      </c>
+      <c r="C10">
+        <v>82</v>
+      </c>
+      <c r="D10">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="E10">
+        <v>1.8</v>
+      </c>
+      <c r="F10">
+        <v>-0.423264205081944</v>
+      </c>
+      <c r="G10">
+        <v>1.99</v>
+      </c>
+      <c r="H10">
+        <v>-0.1509373065564248</v>
+      </c>
+      <c r="I10">
+        <v>67.17000045776368</v>
+      </c>
+      <c r="J10">
+        <v>64.05700035095215</v>
+      </c>
+      <c r="K10">
+        <v>64.07239997863769</v>
+      </c>
+      <c r="L10">
+        <v>60.13969999313355</v>
+      </c>
+      <c r="M10">
+        <v>1.05</v>
+      </c>
+      <c r="N10">
+        <v>1.05</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>42.06</v>
+      </c>
+      <c r="Y10">
+        <v>70.38</v>
+      </c>
+      <c r="Z10">
+        <v>39.37</v>
+      </c>
+      <c r="AA10">
+        <v>42.61</v>
+      </c>
+      <c r="AB10">
+        <v>198.82</v>
+      </c>
+      <c r="AC10">
+        <v>134.04</v>
+      </c>
+      <c r="AD10">
+        <v>2.94</v>
+      </c>
+      <c r="AE10">
+        <v>-91.59999999999999</v>
+      </c>
+      <c r="AF10">
+        <v>3637.84</v>
+      </c>
+      <c r="AG10">
+        <v>-178.72</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK10">
+        <v>55.96172530171316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>92.54032258064517</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>53.63</v>
+      </c>
+      <c r="E11">
+        <v>2.36</v>
+      </c>
+      <c r="F11">
+        <v>0.2706115409540307</v>
+      </c>
+      <c r="G11">
+        <v>2.22</v>
+      </c>
+      <c r="H11">
+        <v>0.196218498523353</v>
+      </c>
+      <c r="I11">
+        <v>51.47600021362305</v>
+      </c>
+      <c r="J11">
+        <v>49.33499984741211</v>
+      </c>
+      <c r="K11">
+        <v>49.77559989929199</v>
+      </c>
+      <c r="L11">
+        <v>46.65785005569458</v>
+      </c>
+      <c r="M11">
+        <v>1.04</v>
+      </c>
+      <c r="N11">
+        <v>1.03</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>29.68</v>
+      </c>
+      <c r="Y11">
+        <v>53.67</v>
+      </c>
+      <c r="Z11">
+        <v>189.84</v>
+      </c>
+      <c r="AA11">
+        <v>3.4</v>
+      </c>
+      <c r="AB11">
+        <v>293.64</v>
+      </c>
+      <c r="AC11">
+        <v>61.64</v>
+      </c>
+      <c r="AD11">
+        <v>3.16</v>
+      </c>
+      <c r="AE11">
+        <v>-15.11</v>
+      </c>
+      <c r="AF11">
+        <v>34.95</v>
+      </c>
+      <c r="AG11">
+        <v>41.1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK11">
+        <v>53.61046042738092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>99.39516129032258</v>
+      </c>
+      <c r="C12">
+        <v>188</v>
+      </c>
+      <c r="D12">
+        <v>123.65</v>
+      </c>
+      <c r="E12">
+        <v>3.17</v>
+      </c>
+      <c r="F12">
+        <v>1.27425324504178</v>
+      </c>
+      <c r="G12">
+        <v>2.91</v>
+      </c>
+      <c r="H12">
+        <v>1.237685913762686</v>
+      </c>
+      <c r="I12">
+        <v>116.1299987792969</v>
+      </c>
+      <c r="J12">
+        <v>108.8645004272461</v>
+      </c>
+      <c r="K12">
+        <v>109.3134001159668</v>
+      </c>
+      <c r="L12">
+        <v>90.56365020751953</v>
+      </c>
+      <c r="M12">
+        <v>1.07</v>
+      </c>
+      <c r="N12">
+        <v>1.06</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>54.1</v>
+      </c>
+      <c r="Y12">
+        <v>124.42</v>
+      </c>
+      <c r="Z12">
+        <v>17.14</v>
+      </c>
+      <c r="AA12">
+        <v>-1.42</v>
+      </c>
+      <c r="AB12">
+        <v>106.05</v>
+      </c>
+      <c r="AC12">
+        <v>175.85</v>
+      </c>
+      <c r="AD12">
+        <v>5.43</v>
+      </c>
+      <c r="AE12">
+        <v>108.82</v>
+      </c>
+      <c r="AF12">
+        <v>26.87</v>
+      </c>
+      <c r="AG12">
+        <v>128.63</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK12">
+        <v>53.55245258764854</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>91.12903225806451</v>
+      </c>
+      <c r="C13">
+        <v>154</v>
+      </c>
+      <c r="D13">
+        <v>257.79</v>
+      </c>
+      <c r="E13">
+        <v>1.37</v>
+      </c>
+      <c r="F13">
+        <v>-0.9560616529309961</v>
+      </c>
+      <c r="G13">
+        <v>1.22</v>
+      </c>
+      <c r="H13">
+        <v>-1.313154567040898</v>
+      </c>
+      <c r="I13">
+        <v>257.2680023193359</v>
+      </c>
+      <c r="J13">
+        <v>254.4255012512207</v>
+      </c>
+      <c r="K13">
+        <v>247.1496008300781</v>
+      </c>
+      <c r="L13">
+        <v>211.3514003753662</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.04</v>
+      </c>
+      <c r="P13">
+        <v>11</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>150.84</v>
+      </c>
+      <c r="Y13">
+        <v>263.31</v>
+      </c>
+      <c r="Z13">
+        <v>161.8</v>
+      </c>
+      <c r="AA13">
+        <v>18.8</v>
+      </c>
+      <c r="AB13">
+        <v>37.04</v>
+      </c>
+      <c r="AC13">
+        <v>102.96</v>
+      </c>
+      <c r="AD13">
+        <v>-120.3</v>
+      </c>
+      <c r="AE13">
+        <v>-35.83</v>
+      </c>
+      <c r="AF13">
+        <v>32.61</v>
+      </c>
+      <c r="AG13">
+        <v>138.52</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK13">
+        <v>52.44961732182784</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>92.13709677419355</v>
+      </c>
+      <c r="C14">
+        <v>434</v>
+      </c>
+      <c r="D14">
+        <v>319.2</v>
+      </c>
+      <c r="E14">
+        <v>1.92</v>
+      </c>
+      <c r="F14">
+        <v>-0.2745765452170924</v>
+      </c>
+      <c r="G14">
+        <v>1.57</v>
+      </c>
+      <c r="H14">
+        <v>-0.7848739940934099</v>
+      </c>
+      <c r="I14">
+        <v>311.6280029296875</v>
+      </c>
+      <c r="J14">
+        <v>301.5605026245117</v>
+      </c>
+      <c r="K14">
+        <v>301.4319995117187</v>
+      </c>
+      <c r="L14">
+        <v>269.8137496185303</v>
+      </c>
+      <c r="M14">
+        <v>1.03</v>
+      </c>
+      <c r="N14">
+        <v>1.03</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>196.77</v>
+      </c>
+      <c r="Y14">
+        <v>323.35</v>
+      </c>
+      <c r="Z14">
+        <v>31.48</v>
+      </c>
+      <c r="AA14">
+        <v>3.9</v>
+      </c>
+      <c r="AB14">
+        <v>20.49</v>
+      </c>
+      <c r="AC14">
+        <v>412.14</v>
+      </c>
+      <c r="AD14">
+        <v>18.07</v>
+      </c>
+      <c r="AE14">
+        <v>77.56</v>
+      </c>
+      <c r="AF14">
+        <v>36.71</v>
+      </c>
+      <c r="AG14">
+        <v>110.98</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK14">
+        <v>48.34511926945184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>93.95161290322581</v>
+      </c>
+      <c r="C15">
+        <v>243</v>
+      </c>
+      <c r="D15">
+        <v>119.34</v>
+      </c>
+      <c r="E15">
+        <v>2.47</v>
+      </c>
+      <c r="F15">
+        <v>0.4069085624968118</v>
+      </c>
+      <c r="G15">
+        <v>3.18</v>
+      </c>
+      <c r="H15">
+        <v>1.645216641465033</v>
+      </c>
+      <c r="I15">
+        <v>119.6720001220703</v>
+      </c>
+      <c r="J15">
+        <v>114.3540004730225</v>
+      </c>
+      <c r="K15">
+        <v>111.5214002990723</v>
+      </c>
+      <c r="L15">
+        <v>92.92435009002685</v>
+      </c>
+      <c r="M15">
+        <v>1.05</v>
+      </c>
+      <c r="N15">
+        <v>1.07</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>65.88</v>
+      </c>
+      <c r="Y15">
+        <v>127.75</v>
+      </c>
+      <c r="Z15">
+        <v>20.39</v>
+      </c>
+      <c r="AA15">
+        <v>171.43</v>
+      </c>
+      <c r="AB15">
+        <v>53.33</v>
+      </c>
+      <c r="AC15">
+        <v>109.71</v>
+      </c>
+      <c r="AD15">
+        <v>-207.94</v>
+      </c>
+      <c r="AE15">
+        <v>122.22</v>
+      </c>
+      <c r="AF15">
+        <v>37.5</v>
+      </c>
+      <c r="AG15">
+        <v>30.1</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK15">
+        <v>46.05035557881475</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16">
+        <v>97.58064516129032</v>
+      </c>
+      <c r="C16">
+        <v>286</v>
+      </c>
+      <c r="D16">
+        <v>112.38</v>
+      </c>
+      <c r="E16">
+        <v>1.64</v>
+      </c>
+      <c r="F16">
+        <v>-0.6215144182350799</v>
+      </c>
+      <c r="G16">
+        <v>2.09</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>113.85</v>
+      </c>
+      <c r="J16">
+        <v>109.3084999084473</v>
+      </c>
+      <c r="K16">
+        <v>103.7092001342773</v>
+      </c>
+      <c r="L16">
+        <v>91.48979999542236</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>1.1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U16" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>58.04</v>
+      </c>
+      <c r="Y16">
+        <v>117.67</v>
+      </c>
+      <c r="Z16">
+        <v>19.06</v>
+      </c>
+      <c r="AA16">
+        <v>26.51</v>
+      </c>
+      <c r="AB16">
+        <v>35.9</v>
+      </c>
+      <c r="AC16">
+        <v>108.04</v>
+      </c>
+      <c r="AD16">
+        <v>87.52</v>
+      </c>
+      <c r="AE16">
+        <v>14.78</v>
+      </c>
+      <c r="AF16">
+        <v>43.97</v>
+      </c>
+      <c r="AG16">
+        <v>25.89</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK16">
+        <v>44.22047743321373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17">
+        <v>98.38709677419355</v>
+      </c>
+      <c r="C17">
+        <v>264</v>
+      </c>
+      <c r="D17">
+        <v>163.16</v>
+      </c>
+      <c r="E17">
+        <v>1.83</v>
+      </c>
+      <c r="F17">
+        <v>-0.386092290115731</v>
+      </c>
+      <c r="G17">
+        <v>2.09</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>161.4480010986328</v>
+      </c>
+      <c r="J17">
+        <v>155.7544998168945</v>
+      </c>
+      <c r="K17">
+        <v>158.4352005004883</v>
+      </c>
+      <c r="L17">
+        <v>135.7386999511719</v>
+      </c>
+      <c r="M17">
+        <v>1.04</v>
+      </c>
+      <c r="N17">
+        <v>1.02</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="Y17">
+        <v>171.12</v>
+      </c>
+      <c r="Z17">
+        <v>42.71</v>
+      </c>
+      <c r="AA17">
+        <v>2.42</v>
+      </c>
+      <c r="AB17">
+        <v>17.33</v>
+      </c>
+      <c r="AC17">
+        <v>143.53</v>
+      </c>
+      <c r="AD17">
+        <v>20.32</v>
+      </c>
+      <c r="AE17">
+        <v>10.11</v>
+      </c>
+      <c r="AF17">
+        <v>38.24</v>
+      </c>
+      <c r="AG17">
+        <v>60</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK17">
+        <v>40.55403544823913</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18">
+        <v>94.55645161290323</v>
+      </c>
+      <c r="C18">
+        <v>101</v>
+      </c>
+      <c r="D18">
+        <v>156.34</v>
+      </c>
+      <c r="E18">
+        <v>2.6</v>
+      </c>
+      <c r="F18">
+        <v>0.5679868606837345</v>
+      </c>
+      <c r="G18">
+        <v>2.52</v>
+      </c>
+      <c r="H18">
+        <v>0.6490304181926279</v>
+      </c>
+      <c r="I18">
+        <v>157.1459991455078</v>
+      </c>
+      <c r="J18">
+        <v>153.9004989624023</v>
+      </c>
+      <c r="K18">
+        <v>151.0341995239258</v>
+      </c>
+      <c r="L18">
+        <v>138.3841999816894</v>
+      </c>
+      <c r="M18">
+        <v>1.02</v>
+      </c>
+      <c r="N18">
+        <v>1.04</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>94.18000000000001</v>
+      </c>
+      <c r="Y18">
+        <v>163.02</v>
+      </c>
+      <c r="Z18">
+        <v>125.58</v>
+      </c>
+      <c r="AA18">
+        <v>26.49</v>
+      </c>
+      <c r="AB18">
+        <v>24.9</v>
+      </c>
+      <c r="AC18">
+        <v>54.47</v>
+      </c>
+      <c r="AD18">
+        <v>13.98</v>
+      </c>
+      <c r="AE18">
+        <v>0.53</v>
+      </c>
+      <c r="AF18">
+        <v>30.34</v>
+      </c>
+      <c r="AG18">
+        <v>17.89</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK18">
+        <v>37.53810990050528</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>94.75806451612904</v>
+      </c>
+      <c r="C19">
+        <v>492</v>
+      </c>
+      <c r="D19">
+        <v>2062.49</v>
+      </c>
+      <c r="E19">
+        <v>1.5</v>
+      </c>
+      <c r="F19">
+        <v>-0.7949833547440734</v>
+      </c>
+      <c r="G19">
+        <v>1.62</v>
+      </c>
+      <c r="H19">
+        <v>-0.7094053408151972</v>
+      </c>
+      <c r="I19">
+        <v>2063.653979492187</v>
+      </c>
+      <c r="J19">
+        <v>2032.39150390625</v>
+      </c>
+      <c r="K19">
+        <v>1926.394799804687</v>
+      </c>
+      <c r="L19">
+        <v>1642.074248046875</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>1.07</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>1111.71</v>
+      </c>
+      <c r="Y19">
+        <v>2110</v>
+      </c>
+      <c r="Z19">
+        <v>39.27</v>
+      </c>
+      <c r="AA19">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB19">
+        <v>12.58</v>
+      </c>
+      <c r="AC19">
+        <v>73.22</v>
+      </c>
+      <c r="AD19">
+        <v>-26.13</v>
+      </c>
+      <c r="AE19">
+        <v>-26.79</v>
+      </c>
+      <c r="AF19">
+        <v>33.08</v>
+      </c>
+      <c r="AG19">
+        <v>77.8</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK19">
+        <v>36.79039498403341</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>90.5241935483871</v>
+      </c>
+      <c r="C20">
+        <v>307</v>
+      </c>
+      <c r="D20">
+        <v>106.52</v>
+      </c>
+      <c r="E20">
+        <v>1.77</v>
+      </c>
+      <c r="F20">
+        <v>-0.460436120048157</v>
+      </c>
+      <c r="G20">
+        <v>1.63</v>
+      </c>
+      <c r="H20">
+        <v>-0.694311610159555</v>
+      </c>
+      <c r="I20">
+        <v>104.4599990844727</v>
+      </c>
+      <c r="J20">
+        <v>100.0099998474121</v>
+      </c>
+      <c r="K20">
+        <v>99.57800003051757</v>
+      </c>
+      <c r="L20">
+        <v>91.86623336791992</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>1.05</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>62.94</v>
+      </c>
+      <c r="Y20">
+        <v>109.12</v>
+      </c>
+      <c r="Z20">
+        <v>19.49</v>
+      </c>
+      <c r="AA20">
+        <v>13.58</v>
+      </c>
+      <c r="AB20">
+        <v>24.27</v>
+      </c>
+      <c r="AC20">
+        <v>36.84</v>
+      </c>
+      <c r="AD20">
+        <v>5.17</v>
+      </c>
+      <c r="AE20">
+        <v>39.6</v>
+      </c>
+      <c r="AF20">
+        <v>-13.37</v>
+      </c>
+      <c r="AG20">
+        <v>13.16</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK20">
+        <v>34.08839466132137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21">
+        <v>94.35483870967742</v>
+      </c>
+      <c r="C21">
+        <v>165</v>
+      </c>
+      <c r="D21">
+        <v>156.57</v>
+      </c>
+      <c r="E21">
+        <v>1.4</v>
+      </c>
+      <c r="F21">
+        <v>-0.9188897379647833</v>
+      </c>
+      <c r="G21">
+        <v>1.27</v>
+      </c>
+      <c r="H21">
+        <v>-1.237685913762685</v>
+      </c>
+      <c r="I21">
+        <v>161.6959991455078</v>
+      </c>
+      <c r="J21">
+        <v>162.271997833252</v>
+      </c>
+      <c r="K21">
+        <v>155.1345993041992</v>
+      </c>
+      <c r="L21">
+        <v>131.9671996688843</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1.04</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>93.08</v>
+      </c>
+      <c r="Y21">
+        <v>169.93</v>
+      </c>
+      <c r="Z21">
+        <v>95.95</v>
+      </c>
+      <c r="AA21">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AB21">
+        <v>1.14</v>
+      </c>
+      <c r="AC21">
+        <v>164.86</v>
+      </c>
+      <c r="AD21">
+        <v>2.17</v>
+      </c>
+      <c r="AE21">
+        <v>20.99</v>
+      </c>
+      <c r="AF21">
+        <v>62</v>
+      </c>
+      <c r="AG21">
+        <v>35.14</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK21">
+        <v>32.19293538820477</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>98.79032258064517</v>
+      </c>
+      <c r="C22">
+        <v>420</v>
+      </c>
+      <c r="D22">
+        <v>217.65</v>
+      </c>
+      <c r="E22">
+        <v>1.43</v>
+      </c>
+      <c r="F22">
+        <v>-0.8817178229985704</v>
+      </c>
+      <c r="G22">
+        <v>1.52</v>
+      </c>
+      <c r="H22">
+        <v>-0.8603426473716224</v>
+      </c>
+      <c r="I22">
+        <v>220.5879974365234</v>
+      </c>
+      <c r="J22">
+        <v>217.3810005187988</v>
+      </c>
+      <c r="K22">
+        <v>206.8938000488281</v>
+      </c>
+      <c r="L22">
+        <v>174.8674997711182</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>1.07</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>109.27</v>
+      </c>
+      <c r="Y22">
+        <v>228.84</v>
+      </c>
+      <c r="Z22">
+        <v>23.59</v>
+      </c>
+      <c r="AA22">
+        <v>12.04</v>
+      </c>
+      <c r="AB22">
+        <v>17.47</v>
+      </c>
+      <c r="AC22">
+        <v>19.49</v>
+      </c>
+      <c r="AD22">
+        <v>5.91</v>
+      </c>
+      <c r="AE22">
+        <v>12.8</v>
+      </c>
+      <c r="AF22">
+        <v>-18.83</v>
+      </c>
+      <c r="AG22">
+        <v>30.51</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK22">
+        <v>28.07510267169616</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23">
+        <v>95.76612903225806</v>
+      </c>
+      <c r="C23">
+        <v>351</v>
+      </c>
+      <c r="D23">
+        <v>105.71</v>
+      </c>
+      <c r="E23">
+        <v>1.93</v>
+      </c>
+      <c r="F23">
+        <v>-0.2621859068950214</v>
+      </c>
+      <c r="G23">
+        <v>1.93</v>
+      </c>
+      <c r="H23">
+        <v>-0.2414996904902799</v>
+      </c>
+      <c r="I23">
+        <v>107.9820007324219</v>
+      </c>
+      <c r="J23">
+        <v>105.578999710083</v>
+      </c>
+      <c r="K23">
+        <v>103.5715995788574</v>
+      </c>
+      <c r="L23">
+        <v>93.52554996490478</v>
+      </c>
+      <c r="M23">
+        <v>1.02</v>
+      </c>
+      <c r="N23">
+        <v>1.04</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>60.6</v>
+      </c>
+      <c r="Y23">
+        <v>111</v>
+      </c>
+      <c r="Z23">
+        <v>33.14</v>
+      </c>
+      <c r="AA23">
+        <v>17.34</v>
+      </c>
+      <c r="AB23">
+        <v>5.07</v>
+      </c>
+      <c r="AC23">
+        <v>38.3</v>
+      </c>
+      <c r="AD23">
+        <v>5.46</v>
+      </c>
+      <c r="AE23">
+        <v>-1.52</v>
+      </c>
+      <c r="AF23">
+        <v>67.09</v>
+      </c>
+      <c r="AG23">
+        <v>-15.96</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK23">
+        <v>25.70543852232563</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24">
+        <v>94.95967741935483</v>
+      </c>
+      <c r="C24">
+        <v>418</v>
+      </c>
+      <c r="D24">
+        <v>365.34</v>
+      </c>
+      <c r="E24">
+        <v>1.24</v>
+      </c>
+      <c r="F24">
+        <v>-1.117139951117919</v>
+      </c>
+      <c r="G24">
+        <v>1.3</v>
+      </c>
+      <c r="H24">
+        <v>-1.192404721795757</v>
+      </c>
+      <c r="I24">
+        <v>366.39599609375</v>
+      </c>
+      <c r="J24">
+        <v>362.8079971313476</v>
+      </c>
+      <c r="K24">
+        <v>343.8961981201172</v>
+      </c>
+      <c r="L24">
+        <v>309.0682006835938</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>1.07</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>217.87</v>
+      </c>
+      <c r="Y24">
+        <v>377.36</v>
+      </c>
+      <c r="Z24">
+        <v>52.23</v>
+      </c>
+      <c r="AA24">
+        <v>2.27</v>
+      </c>
+      <c r="AB24">
+        <v>2.82</v>
+      </c>
+      <c r="AC24">
+        <v>51.5</v>
+      </c>
+      <c r="AD24">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="AE24">
+        <v>27.78</v>
+      </c>
+      <c r="AF24">
+        <v>-10.41</v>
+      </c>
+      <c r="AG24">
+        <v>32.34</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK24">
+        <v>23.65804626096807</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>96.7741935483871</v>
+      </c>
+      <c r="C25">
+        <v>451</v>
+      </c>
+      <c r="D25">
+        <v>220.9</v>
+      </c>
+      <c r="E25">
+        <v>1.11</v>
+      </c>
+      <c r="F25">
+        <v>-1.278218249304842</v>
+      </c>
+      <c r="G25">
+        <v>1.32</v>
+      </c>
+      <c r="H25">
+        <v>-1.162217260484472</v>
+      </c>
+      <c r="I25">
+        <v>225.4160003662109</v>
+      </c>
+      <c r="J25">
+        <v>222.4194999694824</v>
+      </c>
+      <c r="K25">
+        <v>212.157799987793</v>
+      </c>
+      <c r="L25">
+        <v>184.5445498657226</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>1.06</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>123</v>
+      </c>
+      <c r="Y25">
+        <v>231.63</v>
+      </c>
+      <c r="Z25">
+        <v>21.52</v>
+      </c>
+      <c r="AA25">
+        <v>7.02</v>
+      </c>
+      <c r="AB25">
+        <v>6.27</v>
+      </c>
+      <c r="AC25">
+        <v>1.39</v>
+      </c>
+      <c r="AD25">
+        <v>1.43</v>
+      </c>
+      <c r="AE25">
+        <v>-61.17</v>
+      </c>
+      <c r="AF25">
+        <v>370</v>
+      </c>
+      <c r="AG25">
+        <v>-44.44</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK25">
+        <v>8.110731244844265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26">
+        <v>90.7258064516129</v>
+      </c>
+      <c r="C26">
+        <v>181</v>
+      </c>
+      <c r="D26">
+        <v>46.26</v>
+      </c>
+      <c r="E26">
+        <v>1.55</v>
+      </c>
+      <c r="F26">
+        <v>-0.7330301631337185</v>
+      </c>
+      <c r="G26">
+        <v>1.48</v>
+      </c>
+      <c r="H26">
+        <v>-0.9207175699941924</v>
+      </c>
+      <c r="I26">
+        <v>46.8672004699707</v>
+      </c>
+      <c r="J26">
+        <v>46.37320041656494</v>
+      </c>
+      <c r="K26">
+        <v>45.31304008483887</v>
+      </c>
+      <c r="L26">
+        <v>39.7685799407959</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>1.03</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>27.82</v>
+      </c>
+      <c r="Y26">
+        <v>47.97</v>
+      </c>
+      <c r="Z26">
+        <v>4.67</v>
+      </c>
+      <c r="AA26">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AB26">
+        <v>3</v>
+      </c>
+      <c r="AC26">
+        <v>68.97</v>
+      </c>
+      <c r="AD26">
+        <v>11.1</v>
+      </c>
+      <c r="AE26">
+        <v>-38.94</v>
+      </c>
+      <c r="AF26">
+        <v>105.77</v>
+      </c>
+      <c r="AG26">
+        <v>34.48</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK26">
+        <v>27.47242496676621</v>
       </c>
     </row>
   </sheetData>
